--- a/data/PE1_Tabella_B_Progetti_finanziati.xlsx
+++ b/data/PE1_Tabella_B_Progetti_finanziati.xlsx
@@ -724,6 +724,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1387,7 +1388,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026P3T2LW_004</t>
+          <t>2026P3T2LW_005</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
